--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/support_team_structure.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/support_team_structure.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>APAC</t>
         </is>
       </c>
     </row>
@@ -498,11 +498,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>EMEA</t>
         </is>
       </c>
     </row>
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>EMEA</t>
         </is>
       </c>
     </row>
@@ -558,11 +558,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
